--- a/knowledge/自動車アフターマーケット・部品卸/イエローハット_資料/ASIS_Phase1_確認質問票.xlsx
+++ b/knowledge/自動車アフターマーケット・部品卸/イエローハット_資料/ASIS_Phase1_確認質問票.xlsx
@@ -7,15 +7,14 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_使い方" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_整理メモ" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="確認質問票" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="図1_マスタ登録" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="図2_仕入入荷在庫" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="図3_受注引当出荷" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'確認質問票'!$A$5:$J$19</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'確認質問票'!$1:$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'確認質問票'!$A$3:$H$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -24,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,23 +35,17 @@
       <name val="Yu Gothic"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="16"/>
-    </font>
-    <font>
-      <name val="Yu Gothic"/>
-      <color rgb="00666666"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Yu Gothic"/>
-      <color rgb="007A3A10"/>
-      <sz val="9"/>
+      <sz val="14"/>
     </font>
     <font>
       <name val="Yu Gothic"/>
       <b val="1"/>
       <color rgb="0017365D"/>
-      <sz val="11"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Yu Gothic"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Yu Gothic"/>
@@ -62,7 +55,8 @@
     </font>
     <font>
       <name val="Yu Gothic"/>
-      <sz val="10"/>
+      <color rgb="00666666"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Yu Gothic"/>
@@ -73,17 +67,11 @@
     <font>
       <name val="Yu Gothic"/>
       <b val="1"/>
-      <color rgb="007A3A10"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Yu Gothic"/>
-      <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -97,22 +85,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="002E6EB5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002E6EB5"/>
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
     <fill>
@@ -127,17 +105,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F4B183"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00DCE6F1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E2F0D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -167,69 +145,55 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -685,187 +649,272 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="78" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>このファイルの使い方</t>
+          <t>質問の整理方針（社内用・先方には見せない想定）</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>シート構成</t>
+          <t>資料で既に分かっていること（質問にしない／確認言い切りに留める）</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>確認質問票</t>
+          <t>・</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>全質問を1つの表に集約。回答はF列プルダウン、補足はG列。</t>
+          <t>受注は電話・FAX・メール中心のアナログ（設計書p.2）</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>図1_マスタ登録</t>
+          <t>・</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>商品・顧客・適合の登録フロー想定図</t>
+          <t>商流は YH → ジョイフル → 取引先</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>図2_仕入入荷在庫</t>
+          <t>・</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>仕入・入荷・在庫（基幹起点／現場起点）の想定図</t>
+          <t>既存として適合／基幹／倉庫管理／店舗POS／予約 の名前が出る（製品名・中身は未確認）</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>図3_受注引当出荷</t>
+          <t>・</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>受注・引当・出荷の想定図</t>
+          <t>仕入・物流が複雑、原価手計算、取引先別条件の属人化</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr"/>
-      <c r="B8" s="3" t="inlineStr"/>
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>・</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>適合は基幹と別掲 → 適合システムの存在は確定寄り</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>記入手順</t>
-        </is>
-      </c>
+      <c r="A9" s="4" t="inlineStr"/>
+      <c r="B9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>まず Q0-1 / Q0-2（登場人物）を確認</t>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>聞かない／弱める（常識・決めつけ・Phase1外）</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>・</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>図1〜3を見ながら Q1〜Q12 に回答</t>
+          <t>「基幹に手入力していますか？」だけを単問にしない（資料既知。他手段の有無に寄せる）</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>・</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>「一部あっている」「いいえ」の場合はG列に現状を記載</t>
+          <t>「予約システムでも商品／顧客を持っていますか？」はPhase1本丸から外しやすい → 削る</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>・</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>不明な点は「不明／要追加ヒアリング」を選択</t>
+          <t>倉庫＝WMS と決めつけない（倉庫管理の実体を聞く）</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr"/>
-      <c r="B14" s="3" t="inlineStr"/>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>・</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>全システムに商品マスタがある、と決めつけない</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>確定事項（現時点）</t>
-        </is>
-      </c>
+      <c r="A15" s="4" t="inlineStr"/>
+      <c r="B15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>・</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>適合情報は適合システムが正（基幹と別管理）</t>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>今回の質問票に残す本丸</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>・</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>顧客マスタは店舗POSへ連携しない想定</t>
+          <t>卸の管理者（YH／ジョイフル）</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>・</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>商品マスタは基幹→WMS／POS連携の想定</t>
+          <t>取引先の範囲</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>商品／顧客／適合の「正」と持ち方</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>倉庫管理の実体（WMSとは限らない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>実在庫の正・入荷／棚卸のタイミング</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>仕入発注の主体</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>店舗在庫をBtoB出荷に使うか</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>引当・出荷指示・出荷実績の経路</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>自社倉庫／メーカー直送の振分け</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A10:C10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -875,24 +924,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
     <col width="48" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
           <t>イエローハット様　Phase1 AS-IS 確認質問票</t>
@@ -902,740 +949,607 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>目的：Fit&amp;Gap前に現状（AS-IS）を確認する　｜　オレンジ＝想定　｜　回答欄に「はい／いいえ／補足」を記入　｜　図は別シート参照</t>
+          <t>目的：Fit&amp;Gap前に現状（AS-IS）を確認する　｜　資料記載の内容は「想定」に置き、合否と差分だけ伺います</t>
         </is>
       </c>
     </row>
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>想定の要約：商品・顧客マスタは基幹が正（顧客はPOSへ連携しない）／適合は適合システムが正／発注・入荷予定は基幹起点・実在庫・棚卸はWMS・POS起点／電話FAXメール注文を基幹へ手入力</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="24" customHeight="1">
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>枠</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>参照図</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>想定（現状の理解）</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>確認質問</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>回答・補足・現状の説明</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>関連システム</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="52" customHeight="1">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>確認日</t>
-        </is>
-      </c>
-      <c r="B4" s="9" t="n"/>
-      <c r="C4" s="10" t="inlineStr"/>
-      <c r="D4" s="9" t="n"/>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>回答者（貴社）</t>
-        </is>
-      </c>
-      <c r="F4" s="9" t="n"/>
-      <c r="G4" s="9" t="inlineStr"/>
-      <c r="H4" s="9" t="n"/>
-      <c r="I4" s="9" t="n"/>
-      <c r="J4" s="9" t="n"/>
-    </row>
-    <row r="5" ht="34" customHeight="1">
-      <c r="A5" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>枠</t>
-        </is>
-      </c>
-      <c r="C5" s="11" t="inlineStr">
-        <is>
-          <t>参照図</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>登場人物</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>卸事業の管理者はイエローハット様／ジョイフル様／両方のいずれか</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>タイヤ・その他カー用品の卸事業の管理者は、イエローハット様／ジョイフル様／どちらも、のどれでしょうか。役割分担があれば教えてください。</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr"/>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>最優先</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="52" customHeight="1">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>登場人物</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>想定（現状の理解）</t>
+          <t>取引先＝ディーラー／整備工場／YH FC加盟店／中古車販売店</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>確認質問</t>
-        </is>
-      </c>
-      <c r="F5" s="11" t="inlineStr">
-        <is>
-          <t>回答
-（はい／いいえ／一部）</t>
-        </is>
-      </c>
-      <c r="G5" s="11" t="inlineStr">
-        <is>
-          <t>補足・現状の説明</t>
-        </is>
-      </c>
-      <c r="H5" s="11" t="inlineStr">
-        <is>
-          <t>関連システム</t>
-        </is>
-      </c>
-      <c r="I5" s="11" t="inlineStr">
-        <is>
-          <t>優先</t>
-        </is>
-      </c>
-      <c r="J5" s="11" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="48" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>Q0-1</t>
+          <t>Phase1の取引先様は、ディーラー／整備工場／イエローハット様FC加盟店／中古車販売店で合っておりますか。他にございますでしょうか。</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr"/>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>範囲確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="52" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>登場人物</t>
-        </is>
-      </c>
-      <c r="C6" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D6" s="15" t="inlineStr">
-        <is>
-          <t>卸事業の管理者はYH／ジョイフル／両方のいずれか</t>
-        </is>
-      </c>
-      <c r="E6" s="15" t="inlineStr">
-        <is>
-          <t>タイヤ・その他カー用品の卸事業の管理者は、イエローハット様／ジョイフル様／どちらも、のどれですか？ 役割分担があれば教えてください</t>
-        </is>
-      </c>
-      <c r="F6" s="16" t="inlineStr"/>
-      <c r="G6" s="17" t="inlineStr"/>
-      <c r="H6" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I6" s="18" t="inlineStr">
-        <is>
-          <t>最優先</t>
-        </is>
-      </c>
-      <c r="J6" s="15" t="inlineStr">
-        <is>
-          <t>最初に潰す</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="48" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>Q0-2</t>
+          <t>マスタ</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>図1</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>商品マスタの正は基幹。他システムへ連携または反映している</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>商品マスタは基幹を正として管理している理解で合っておりますか。倉庫管理・店舗POS等へは、どのように反映されていますか（自動連携／CSV／手動）。</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr"/>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>基幹／倉庫／POS</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>※全システム保有とは決めつけない</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="52" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>登場人物</t>
-        </is>
-      </c>
-      <c r="C7" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D7" s="15" t="inlineStr">
-        <is>
-          <t>取引先＝ディーラー／整備工場／YH FC／中古車販売店</t>
-        </is>
-      </c>
-      <c r="E7" s="15" t="inlineStr">
-        <is>
-          <t>Phase1の取引先は、ディーラー／整備工場／YH FC加盟店／中古車販売店で合っていますか？ ほかにいますか？</t>
-        </is>
-      </c>
-      <c r="F7" s="16" t="inlineStr"/>
-      <c r="G7" s="17" t="inlineStr"/>
-      <c r="H7" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I7" s="18" t="inlineStr">
-        <is>
-          <t>最優先</t>
-        </is>
-      </c>
-      <c r="J7" s="15" t="inlineStr">
-        <is>
-          <t>範囲確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="48" customHeight="1">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
-      <c r="B8" s="19" t="inlineStr">
-        <is>
           <t>マスタ</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>図1</t>
         </is>
       </c>
-      <c r="D8" s="15" t="inlineStr">
-        <is>
-          <t>商品マスタの正は基幹（JAN・価格・原価含む）</t>
-        </is>
-      </c>
-      <c r="E8" s="15" t="inlineStr">
-        <is>
-          <t>商品マスタの「正」は基幹で合っていますか？ JAN・価格・原価も基幹で管理していますか？</t>
-        </is>
-      </c>
-      <c r="F8" s="16" t="inlineStr"/>
-      <c r="G8" s="17" t="inlineStr"/>
-      <c r="H8" s="14" t="inlineStr">
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>顧客マスタ（掛率・与信・請求含む）の正は基幹。店舗POSへは連携しない</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>顧客マスタは基幹を正として管理している理解で合っておりますか。店舗POSへは連携していない、でよろしいでしょうか。</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="inlineStr"/>
+      <c r="G7" s="10" t="inlineStr">
         <is>
           <t>基幹</t>
         </is>
       </c>
-      <c r="I8" s="14" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="J8" s="15" t="inlineStr">
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>顧客≠POS</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="52" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>マスタ</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>図1</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="48" customHeight="1">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>Q2</t>
-        </is>
-      </c>
-      <c r="B9" s="19" t="inlineStr">
-        <is>
-          <t>マスタ</t>
-        </is>
-      </c>
-      <c r="C9" s="14" t="inlineStr">
-        <is>
-          <t>図1</t>
-        </is>
-      </c>
-      <c r="D9" s="15" t="inlineStr">
-        <is>
-          <t>顧客マスタ（掛率・与信・請求）の正は基幹。店舗POSへは連携しない</t>
-        </is>
-      </c>
-      <c r="E9" s="15" t="inlineStr">
-        <is>
-          <t>顧客マスタの「正」は基幹で合っていますか？ 店舗POSには顧客マスタを連携していない理解で合っていますか？</t>
-        </is>
-      </c>
-      <c r="F9" s="16" t="inlineStr"/>
-      <c r="G9" s="17" t="inlineStr"/>
-      <c r="H9" s="14" t="inlineStr">
-        <is>
-          <t>基幹／POS</t>
-        </is>
-      </c>
-      <c r="I9" s="14" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="J9" s="15" t="inlineStr">
-        <is>
-          <t>顧客≠POS</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="48" customHeight="1">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>Q3</t>
-        </is>
-      </c>
-      <c r="B10" s="19" t="inlineStr">
-        <is>
-          <t>マスタ</t>
-        </is>
-      </c>
-      <c r="C10" s="14" t="inlineStr">
-        <is>
-          <t>図1</t>
-        </is>
-      </c>
-      <c r="D10" s="15" t="inlineStr">
-        <is>
-          <t>適合情報は適合システムが正（基幹と別）。JAN等で紐付け</t>
-        </is>
-      </c>
-      <c r="E10" s="15" t="inlineStr">
-        <is>
-          <t>適合情報は適合システムが「正」で合っていますか？ 基幹商品との紐付け方法（JAN等）とメンテ担当を教えてください</t>
-        </is>
-      </c>
-      <c r="F10" s="16" t="inlineStr"/>
-      <c r="G10" s="17" t="inlineStr"/>
-      <c r="H10" s="14" t="inlineStr">
-        <is>
-          <t>適合システム</t>
-        </is>
-      </c>
-      <c r="I10" s="14" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="J10" s="15" t="inlineStr">
-        <is>
-          <t>No.7別掲</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="48" customHeight="1">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>Q4</t>
-        </is>
-      </c>
-      <c r="B11" s="19" t="inlineStr">
-        <is>
-          <t>マスタ</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="inlineStr">
-        <is>
-          <t>図1</t>
-        </is>
-      </c>
-      <c r="D11" s="15" t="inlineStr">
-        <is>
-          <t>商品マスタのみ基幹→WMS・POSへ連携。顧客は基幹に留まる。WMSへ出荷先コードがある可能性</t>
-        </is>
-      </c>
-      <c r="E11" s="15" t="inlineStr">
-        <is>
-          <t>商品マスタは基幹からWMS・店舗POSへどう連携していますか？（API／CSV／手動） WMSへ出荷先として顧客コードを出すことはありますか？</t>
-        </is>
-      </c>
-      <c r="F11" s="16" t="inlineStr"/>
-      <c r="G11" s="17" t="inlineStr"/>
-      <c r="H11" s="14" t="inlineStr">
-        <is>
-          <t>基幹／WMS／POS</t>
-        </is>
-      </c>
-      <c r="I11" s="14" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="J11" s="15" t="inlineStr">
-        <is>
-          <t>商品のみ連携</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="48" customHeight="1">
-      <c r="A12" s="12" t="inlineStr">
-        <is>
-          <t>Q5</t>
-        </is>
-      </c>
-      <c r="B12" s="19" t="inlineStr">
-        <is>
-          <t>マスタ</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="inlineStr">
-        <is>
-          <t>図1</t>
-        </is>
-      </c>
-      <c r="D12" s="15" t="inlineStr">
-        <is>
-          <t>登録主体はYHまたはジョイフル（要確認）。店舗独自商品のPOS起点登録があるかも</t>
-        </is>
-      </c>
-      <c r="E12" s="15" t="inlineStr">
-        <is>
-          <t>商品・顧客の登録主体はイエローハット様／ジョイフル様のどちらですか？ 店舗独自商品がPOS起点で登録されることはありますか？</t>
-        </is>
-      </c>
-      <c r="F12" s="16" t="inlineStr"/>
-      <c r="G12" s="17" t="inlineStr"/>
-      <c r="H12" s="14" t="inlineStr">
-        <is>
-          <t>基幹／POS</t>
-        </is>
-      </c>
-      <c r="I12" s="14" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="J12" s="15" t="inlineStr">
-        <is>
-          <t>管理者確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="48" customHeight="1">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>Q6</t>
-        </is>
-      </c>
-      <c r="B13" s="20" t="inlineStr">
-        <is>
-          <t>仕入・在庫</t>
-        </is>
-      </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>適合情報は適合システムが正（基幹と別管理）。注文時に参照／突合</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>適合情報は適合システムが正、という理解で合っておりますか。基幹の商品との紐付け方法と、受注時の突合方法をご教示ください。</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="inlineStr"/>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>適合／基幹</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>資料No.7で別掲</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="52" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>倉庫・在庫</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>図2</t>
         </is>
       </c>
-      <c r="D13" s="15" t="inlineStr">
-        <is>
-          <t>倉庫実在庫の正＝WMS、店舗実在庫の正＝POS。基幹は集約</t>
-        </is>
-      </c>
-      <c r="E13" s="15" t="inlineStr">
-        <is>
-          <t>倉庫の実在庫の「正」は基幹／WMSのどちらですか？ 店舗の実在庫の「正」は基幹／POSのどちらですか？</t>
-        </is>
-      </c>
-      <c r="F13" s="16" t="inlineStr"/>
-      <c r="G13" s="17" t="inlineStr"/>
-      <c r="H13" s="14" t="inlineStr">
-        <is>
-          <t>基幹／WMS／POS</t>
-        </is>
-      </c>
-      <c r="I13" s="14" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="J13" s="15" t="inlineStr">
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>資料上の「倉庫管理」は専用WMSとは限らない（基幹機能／自社／3PL等の可能性）</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>倉庫での入荷・在庫・出荷は、どの仕組みで管理されていますか。専用WMS／基幹の倉庫機能／自社システム／物流委託先システム／Excel・紙運用など、該当するものをご教示ください。</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr"/>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>倉庫管理</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>WMS決めつけ回避</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="52" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>倉庫・在庫</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>図2</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>倉庫実在庫の正＝倉庫側、店舗実在庫の正＝POS。基幹は集約</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>倉庫の実在庫は倉庫側、店舗の実在庫はPOSが正で、基幹はそれらを集約しているイメージで合っておりますか。</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="inlineStr"/>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>基幹／倉庫／POS</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
         <is>
           <t>在庫の正</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="48" customHeight="1">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>Q7</t>
-        </is>
-      </c>
-      <c r="B14" s="20" t="inlineStr">
-        <is>
-          <t>仕入・在庫</t>
-        </is>
-      </c>
-      <c r="C14" s="14" t="inlineStr">
+    <row r="11" ht="52" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>倉庫・在庫</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
         <is>
           <t>図2</t>
         </is>
       </c>
-      <c r="D14" s="15" t="inlineStr">
-        <is>
-          <t>仕入発注はYH／ジョイフル担当が基幹（またはアナログ）で実施。入荷予定は基幹に登録</t>
-        </is>
-      </c>
-      <c r="E14" s="15" t="inlineStr">
-        <is>
-          <t>仕入発注は誰が・どのシステムで行いますか？（YH本部／ジョイフル／各店舗／アナログ） 入荷予定は基幹に登録されますか？</t>
-        </is>
-      </c>
-      <c r="F14" s="16" t="inlineStr"/>
-      <c r="G14" s="17" t="inlineStr"/>
-      <c r="H14" s="14" t="inlineStr">
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>入荷時に倉庫／POSへ入力して基幹へ返す、または棚卸タイミングで合わせる、のいずれか</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>入荷後の在庫反映は、入荷の都度（倉庫／POS入力→基幹反映）でしょうか。それとも棚卸等のタイミングで合わせていますか。</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="inlineStr"/>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>基幹／倉庫／POS</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>運用タイミング</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="52" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>倉庫・在庫</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>図2</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>仕入発注の主体・手段は未確認（本部／ジョイフル／店舗／アナログ混在の可能性）</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>仕入発注は誰が、どの手段・システムで行っていますか。現在の運用をご教示ください。</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="inlineStr"/>
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t>基幹等</t>
+        </is>
+      </c>
+      <c r="H12" s="10" t="inlineStr">
+        <is>
+          <t>オープン質問</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="52" customHeight="1">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>倉庫・在庫</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>図2</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>店舗在庫をBtoB卸出荷に使うかは未確認（将来やりたい話と現状は分けて確認）</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>店舗の在庫を、いまのBtoB卸注文の出荷・引当に利用していますか。利用している場合、対象店舗の範囲を教えてください。</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="inlineStr"/>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>POS／基幹</t>
+        </is>
+      </c>
+      <c r="H13" s="10" t="inlineStr">
+        <is>
+          <t>設計に効く</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="52" customHeight="1">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>受注・出荷</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>図3</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>電話・FAX・メールが中心（資料記載）。基幹へ担当者が起票</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>受注は電話・FAX・メールが中心で、担当者が基幹へ起票している理解で合っておりますか。他に受注手段（EDI・既存WEB等）はございますか。</t>
+        </is>
+      </c>
+      <c r="F14" s="12" t="inlineStr"/>
+      <c r="G14" s="10" t="inlineStr">
         <is>
           <t>基幹</t>
         </is>
       </c>
-      <c r="I14" s="14" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="J14" s="15" t="inlineStr">
-        <is>
-          <t>発注起点</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="48" customHeight="1">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>Q8</t>
-        </is>
-      </c>
-      <c r="B15" s="20" t="inlineStr">
-        <is>
-          <t>仕入・在庫</t>
-        </is>
-      </c>
-      <c r="C15" s="14" t="inlineStr">
-        <is>
-          <t>図2</t>
-        </is>
-      </c>
-      <c r="D15" s="15" t="inlineStr">
-        <is>
-          <t>入荷検品はWMS／POS入力→基幹へ実績連携。販売可能在庫は基幹で計算</t>
-        </is>
-      </c>
-      <c r="E15" s="15" t="inlineStr">
-        <is>
-          <t>入荷検品はWMS／POSで入力し、実績は基幹へ自動連携されますか？ 全拠点の販売可能在庫はどこで計算していますか？</t>
-        </is>
-      </c>
-      <c r="F15" s="16" t="inlineStr"/>
-      <c r="G15" s="17" t="inlineStr"/>
-      <c r="H15" s="14" t="inlineStr">
-        <is>
-          <t>基幹／WMS／POS</t>
-        </is>
-      </c>
-      <c r="I15" s="14" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="J15" s="15" t="inlineStr">
-        <is>
-          <t>実績戻し</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="48" customHeight="1">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>Q9</t>
-        </is>
-      </c>
-      <c r="B16" s="20" t="inlineStr">
-        <is>
-          <t>仕入・在庫</t>
-        </is>
-      </c>
-      <c r="C16" s="14" t="inlineStr">
-        <is>
-          <t>図2</t>
-        </is>
-      </c>
-      <c r="D16" s="15" t="inlineStr">
-        <is>
-          <t>棚卸は現場（WMS／POS）で入力し、差異を基幹へ連携</t>
-        </is>
-      </c>
-      <c r="E16" s="15" t="inlineStr">
-        <is>
-          <t>棚卸はWMS／POSで入力し、差異を基幹へ連携しますか？ 在庫調整の承認者と、最終的な在庫の「正」はどこですか？</t>
-        </is>
-      </c>
-      <c r="F16" s="16" t="inlineStr"/>
-      <c r="G16" s="17" t="inlineStr"/>
-      <c r="H16" s="14" t="inlineStr">
-        <is>
-          <t>WMS／POS／基幹</t>
-        </is>
-      </c>
-      <c r="I16" s="14" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="J16" s="15" t="inlineStr">
-        <is>
-          <t>棚卸</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="48" customHeight="1">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>Q10</t>
-        </is>
-      </c>
-      <c r="B17" s="21" t="inlineStr">
+      <c r="H14" s="10" t="inlineStr">
+        <is>
+          <t>資料既知は確認止め</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="52" customHeight="1">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
         <is>
           <t>受注・出荷</t>
         </is>
       </c>
-      <c r="C17" s="14" t="inlineStr">
+      <c r="C15" s="10" t="inlineStr">
         <is>
           <t>図3</t>
         </is>
       </c>
-      <c r="D17" s="15" t="inlineStr">
-        <is>
-          <t>取引先から電話・FAX・メールで注文→担当者が基幹へ手入力</t>
-        </is>
-      </c>
-      <c r="E17" s="15" t="inlineStr">
-        <is>
-          <t>電話・FAX・メール注文は、担当者が基幹へ手入力していますか？ おおよその比率と、他の受注手段があれば教えてください</t>
-        </is>
-      </c>
-      <c r="F17" s="16" t="inlineStr"/>
-      <c r="G17" s="17" t="inlineStr"/>
-      <c r="H17" s="14" t="inlineStr">
-        <is>
-          <t>基幹</t>
-        </is>
-      </c>
-      <c r="I17" s="14" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="J17" s="15" t="inlineStr">
-        <is>
-          <t>手入力</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="48" customHeight="1">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>Q11</t>
-        </is>
-      </c>
-      <c r="B18" s="21" t="inlineStr">
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>引当は基幹側で行い、倉庫／店舗へ連携している可能性</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>受注後の在庫引当は、どのシステムで行い、倉庫側・店舗側へどのように連携していますか。</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="inlineStr"/>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>基幹／倉庫／POS</t>
+        </is>
+      </c>
+      <c r="H15" s="10" t="inlineStr">
+        <is>
+          <t>引当</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="52" customHeight="1">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
         <is>
           <t>受注・出荷</t>
         </is>
       </c>
-      <c r="C18" s="14" t="inlineStr">
+      <c r="C16" s="10" t="inlineStr">
         <is>
           <t>図3</t>
         </is>
       </c>
-      <c r="D18" s="15" t="inlineStr">
-        <is>
-          <t>基幹で引当・出荷指示。店舗POSがBtoB引当を処理できるとは限らない</t>
-        </is>
-      </c>
-      <c r="E18" s="15" t="inlineStr">
-        <is>
-          <t>引当は基幹／WMS／店舗POSのどこで実行しますか？ 店舗出荷時の指示先はPOSですか、別システムですか？</t>
-        </is>
-      </c>
-      <c r="F18" s="16" t="inlineStr"/>
-      <c r="G18" s="17" t="inlineStr"/>
-      <c r="H18" s="14" t="inlineStr">
-        <is>
-          <t>基幹／WMS／POS</t>
-        </is>
-      </c>
-      <c r="I18" s="14" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="J18" s="15" t="inlineStr">
-        <is>
-          <t>引当場所</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="48" customHeight="1">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>Q12</t>
-        </is>
-      </c>
-      <c r="B19" s="21" t="inlineStr">
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>自社倉庫出荷とメーカー直送が混在（資料記載）。振分け運用は未確認</t>
+        </is>
+      </c>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>自社倉庫出荷とメーカー直送の使い分けは、誰が・何を見て判断していますか。</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="inlineStr"/>
+      <c r="G16" s="10" t="inlineStr">
+        <is>
+          <t>基幹／倉庫</t>
+        </is>
+      </c>
+      <c r="H16" s="10" t="inlineStr">
+        <is>
+          <t>資料の混在を深掘り</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="52" customHeight="1">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
         <is>
           <t>受注・出荷</t>
         </is>
       </c>
-      <c r="C19" s="14" t="inlineStr">
+      <c r="C17" s="10" t="inlineStr">
         <is>
           <t>図3</t>
         </is>
       </c>
-      <c r="D19" s="15" t="inlineStr">
-        <is>
-          <t>出荷実績・送り状・在庫減算をWMS／POSで登録し基幹へ戻す。振分けは担当者</t>
-        </is>
-      </c>
-      <c r="E19" s="15" t="inlineStr">
-        <is>
-          <t>出荷完了・送り状番号・在庫減算はどこで登録し、基幹へどう戻しますか？ 自社倉庫／メーカー直送の振分けは誰が行いますか？</t>
-        </is>
-      </c>
-      <c r="F19" s="16" t="inlineStr"/>
-      <c r="G19" s="17" t="inlineStr"/>
-      <c r="H19" s="14" t="inlineStr">
-        <is>
-          <t>基幹／WMS／POS</t>
-        </is>
-      </c>
-      <c r="I19" s="14" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="J19" s="15" t="inlineStr">
-        <is>
-          <t>実績・振分け</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="22" t="inlineStr">
-        <is>
-          <t>記入のお願い：F列（回答）はプルダウン選択、G列に補足を自由記述。図の詳細は「図1_マスタ登録」「図2_仕入入荷在庫」「図3_受注引当出荷」シートを参照。</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="23" t="inlineStr">
-        <is>
-          <t>重点3点：①卸事業の管理主体（YH／ジョイフル）　②在庫の「正」がどのシステムか　③店舗POSがBtoB出荷にどう関わるか</t>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>出荷指示〜実績登録の経路は未確認</t>
+        </is>
+      </c>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>出荷指示と出荷実績（在庫減算・送り状等）は、現在どのように運用していますか。どのシステムに入力し、基幹へどう反映されますか。</t>
+        </is>
+      </c>
+      <c r="F17" s="12" t="inlineStr"/>
+      <c r="G17" s="10" t="inlineStr">
+        <is>
+          <t>基幹／倉庫／POS</t>
+        </is>
+      </c>
+      <c r="H17" s="10" t="inlineStr">
+        <is>
+          <t>出荷オペ</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>重点3点：①卸の管理主体（YH／ジョイフル）　②在庫・倉庫管理の正と実体　③店舗在庫がBtoB出荷に関わるか／引当・出荷の経路</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="17" t="inlineStr">
+        <is>
+          <t>聞かない方針：資料に明記済みの事実の再質問（アナログ受注の有無だけ等）、予約システムの商品/顧客保有、WMS前提の決めつけ、全システムにマスタがある前提</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:J19"/>
-  <mergeCells count="9">
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="A22:J22"/>
-    <mergeCell ref="G4:J4"/>
-    <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A21:J21"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="C4:D4"/>
+  <autoFilter ref="A3:H17"/>
+  <mergeCells count="4">
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="F6:F19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="回答" error="リストから選択してください" promptTitle="確認結果" prompt="回答を選択" type="list">
-      <formula1>"はい,いいえ,一部あっている,不明,要追加ヒアリング"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1652,7 +1566,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="24" t="inlineStr">
+      <c r="A1" s="18" t="inlineStr">
         <is>
           <t>図1：マスタ登録フロー（商品・顧客・適合）
 顧客はPOSへ連携しない想定／適合は適合システムが正</t>
@@ -1660,7 +1574,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="25" t="inlineStr">
+      <c r="A2" s="19" t="inlineStr">
         <is>
           <t>関連質問は「確認質問票」シートの参照図列を参照</t>
         </is>
@@ -1689,15 +1603,15 @@
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="24" t="inlineStr">
+      <c r="A1" s="18" t="inlineStr">
         <is>
           <t>図2：仕入・入荷・在庫フロー
-予定・発注＝基幹起点／実入荷・棚卸＝現場（WMS・POS）起点</t>
+倉庫＝WMSとは限らない／予定は基幹・実在庫は現場起点の仮説</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="25" t="inlineStr">
+      <c r="A2" s="19" t="inlineStr">
         <is>
           <t>関連質問は「確認質問票」シートの参照図列を参照</t>
         </is>
@@ -1726,15 +1640,15 @@
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="24" t="inlineStr">
+      <c r="A1" s="18" t="inlineStr">
         <is>
           <t>図3：受注・引当・出荷フロー
-手入力・引当場所・店舗POS関与・実績戻しを確認</t>
+手入力確認止め＋引当・出荷経路・直送振分けを確認</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="25" t="inlineStr">
+      <c r="A2" s="19" t="inlineStr">
         <is>
           <t>関連質問は「確認質問票」シートの参照図列を参照</t>
         </is>

--- a/knowledge/自動車アフターマーケット・部品卸/イエローハット_資料/ASIS_Phase1_確認質問票.xlsx
+++ b/knowledge/自動車アフターマーケット・部品卸/イエローハット_資料/ASIS_Phase1_確認質問票.xlsx
@@ -293,6 +293,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -323,6 +326,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -353,6 +359,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -649,7 +658,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -909,12 +918,56 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>追加深掘り（店舗在庫×BtoB）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>・</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>仮説A：取引先ごとに対応店舗があり、倉庫 or 対応店舗から出荷</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>・</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>仮説B：BtoB卸は倉庫出荷のみ。店舗関与はPhase2の作業依頼</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>・</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>質問は二者択一＋その他で聞く。①なら対応店舗の決め方と店舗在庫引当の有無まで</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
+    <mergeCell ref="A10:C10"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A27:B27"/>
     <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A10:C10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1337,7 +1390,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="52" customHeight="1">
+    <row r="13" ht="78" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
           <t>10</t>
@@ -1355,12 +1408,16 @@
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>店舗在庫をBtoB卸出荷に使うかは未確認（将来やりたい話と現状は分けて確認）</t>
+          <t>取引先ごとに対応店舗があり、倉庫または対応店舗から出荷している可能性。一方で、BtoB卸は倉庫出荷のみで、店舗関与はPhase2（作業依頼）の話、という可能性もある</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>店舗の在庫を、いまのBtoB卸注文の出荷・引当に利用していますか。利用している場合、対象店舗の範囲を教えてください。</t>
+          <t>BtoB卸の出荷元について確認させてください。
+① 取引先ごとに対応店舗が決まっており、倉庫またはその対応店舗から出荷している
+② BtoB卸は倉庫出荷のみで、店舗は関与しない（店舗関与はPhase2の作業依頼側）
+③ その他
+現状はどれに近いでしょうか。①の場合、対応店舗の決め方と、店舗在庫を引当・出荷に使っているかも教えてください。</t>
         </is>
       </c>
       <c r="F13" s="12" t="inlineStr"/>
@@ -1371,7 +1428,7 @@
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>設計に効く</t>
+          <t>出荷元の切り分け（Phase1/2）</t>
         </is>
       </c>
     </row>

--- a/knowledge/自動車アフターマーケット・部品卸/イエローハット_資料/ASIS_Phase1_確認質問票.xlsx
+++ b/knowledge/自動車アフターマーケット・部品卸/イエローハット_資料/ASIS_Phase1_確認質問票.xlsx
@@ -279,6 +279,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -309,6 +312,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -339,6 +345,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -798,7 +807,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="62" customHeight="1">
+    <row r="7" ht="68" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>4</t>
@@ -811,23 +820,24 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>顧客マスタ（掛率・与信・請求条件含む）の管理システム（正）は基幹。店舗POSには連携していない</t>
+          <t>顧客マスタ（掛率・与信・請求条件含む）の管理システム（正）は基幹。店舗POSには連携していない。一方で、予約システム側にも顧客情報を保持している可能性がある</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>顧客マスタは基幹で管理（正）している理解で合っておりますか。店舗POSには顧客マスタを連携していない、で合っておりますか。</t>
+          <t>顧客マスタは基幹で管理（正）している理解で合っておりますか。店舗POSには顧客マスタを連携していない、で合っておりますか。
+また、予約システムでも顧客情報を保持されておりますか。保持している場合、基幹の顧客マスタとの関係（正はどちらか／連携の有無）を教えてください。</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr"/>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>基幹</t>
+          <t>基幹／POS／予約</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>顧客の管理システム＝基幹</t>
+          <t>予約側の顧客保持を確認</t>
         </is>
       </c>
     </row>

--- a/knowledge/自動車アフターマーケット・部品卸/イエローハット_資料/ASIS_Phase1_確認質問票.xlsx
+++ b/knowledge/自動車アフターマーケット・部品卸/イエローハット_資料/ASIS_Phase1_確認質問票.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="図3_受注引当出荷" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'確認質問票'!$A$3:$G$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'確認質問票'!$A$3:$F$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -279,9 +279,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -312,9 +309,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -345,9 +339,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -644,16 +635,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
-    <col width="52" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="66" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -666,7 +656,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>聞き方の前提：「こう理解しておりますが、合っておりますか？」　｜　差分があれば回答欄へご記入ください　｜　図は別シート参照</t>
+          <t>弊社にて現状をこのように理解しております。相違があれば回答欄にご記入ください。　｜　図は別シート参照</t>
         </is>
       </c>
     </row>
@@ -683,31 +673,26 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>想定（現状の理解）</t>
+          <t>確認質問</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>確認質問</t>
+          <t>回答・補足・現状の説明</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>回答・補足・現状の説明</t>
+          <t>関連システム</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>関連システム</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="50" customHeight="1">
+    <row r="4" ht="52" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
           <t>1</t>
@@ -720,60 +705,50 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>卸事業の管理者は、イエローハット様／ジョイフル様／両方のいずれか</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>タイヤ・その他カー用品の卸事業の管理者は、イエローハット様／ジョイフル様／どちらも、のどれでしょうか。役割分担があれば教えてください。</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr"/>
+          <t>タイヤ・その他カー用品の卸事業の管理者は、イエローハット様／ジョイフル様／どちらでしょうか。両社で役割分担がある場合は、その内容も教えてください。</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr"/>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
+          <t>最優先</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>登場人物</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Phase1の取引先は、ディーラー／整備工場／イエローハット様FC加盟店／中古車販売店を想定しております。この範囲で相違ないか、他に対象があればご教示ください。</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr"/>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
-        <is>
-          <t>最優先</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="50" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>登場人物</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>Phase1の取引先は、ディーラー／整備工場／イエローハット様FC加盟店／中古車販売店</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>取引先様は、ディーラー／整備工場／イエローハット様FC加盟店／中古車販売店で合っておりますか。他にございますでしょうか。</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr"/>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="8" t="inlineStr">
-        <is>
           <t>範囲確認</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="62" customHeight="1">
+    <row r="6" ht="58" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>3</t>
@@ -786,28 +761,22 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>商品マスタの管理システム（正）は基幹。店舗POS・倉庫管理側にも商品情報があり、基幹から反映している。適合システムは適合情報の管理（商品マスタ本体ではない）</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>商品マスタは基幹で管理（正）している理解で合っておりますか。
-また、商品情報を保持しているシステムは「基幹／店舗POS／倉庫管理」で合っておりますか。基幹から各システムへの反映方法（自動連携／CSV／手動）も、合っているかご確認ください。</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr"/>
+          <t>商品マスタは基幹で管理（正）し、店舗POS・倉庫管理へ反映していると理解しております。商品情報を保持するシステムがこの3つで正しいか、また基幹からの反映方法（自動連携／CSV／手動）をご教示ください。</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr"/>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>基幹／POS／倉庫</t>
+        </is>
+      </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>基幹／POS／倉庫</t>
-        </is>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>どのシステムで管理かを明確化</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="68" customHeight="1">
+          <t>管理システムを明確化</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="64" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>4</t>
@@ -820,28 +789,22 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>顧客マスタ（掛率・与信・請求条件含む）の管理システム（正）は基幹。店舗POSには連携していない。一方で、予約システム側にも顧客情報を保持している可能性がある</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>顧客マスタは基幹で管理（正）している理解で合っておりますか。店舗POSには顧客マスタを連携していない、で合っておりますか。
-また、予約システムでも顧客情報を保持されておりますか。保持している場合、基幹の顧客マスタとの関係（正はどちらか／連携の有無）を教えてください。</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr"/>
+          <t>顧客マスタ（掛率・与信・請求条件含む）は基幹で管理（正）し、店舗POSへは連携していないと理解しております。加えて、予約システムでも顧客情報を保持されているか、保持されている場合の基幹との関係（正・連携有無）を教えてください。</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr"/>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>基幹／POS／予約</t>
+        </is>
+      </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>基幹／POS／予約</t>
-        </is>
-      </c>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t>予約側の顧客保持を確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="62" customHeight="1">
+          <t>予約側の顧客保持</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="52" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>5</t>
@@ -854,28 +817,22 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>適合情報の管理システム（正）は適合システム。基幹の商品と紐付け、受注入力時に突合している</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>適合情報は適合システムで管理（正）している理解で合っておりますか。
-基幹の商品と紐付けたうえで、基幹への注文入力時に適合情報の突合を行っている、で合っておりますか。</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr"/>
+          <t>適合情報は適合システムで管理（正）し、基幹の商品と紐付けたうえで、基幹への注文入力時に突合していると理解しております。この流れで相違ないかご確認ください。</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr"/>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>適合／基幹</t>
+        </is>
+      </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>適合／基幹</t>
-        </is>
-      </c>
-      <c r="G8" s="8" t="inlineStr">
-        <is>
-          <t>適合の管理システム＝適合</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="50" customHeight="1">
+          <t>適合＝適合システム</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
           <t>6</t>
@@ -888,28 +845,22 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>倉庫での入荷・在庫・出荷は「倉庫管理」の仕組みで行っている（専用WMSとは限らず、基幹の倉庫機能／自社／物流委託先等の可能性あり）。店舗在庫は店舗POSが管理</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>倉庫側の在庫・入出荷は倉庫管理の仕組み、店舗側の在庫は店舗POSで管理している理解で合っておりますか。
-倉庫管理が専用WMSか、基幹の機能か、物流委託先システムか等、該当があれば補足ください。</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr"/>
+          <t>倉庫側の在庫・入出荷は倉庫管理の仕組み、店舗側の在庫は店舗POSで管理していると理解しております。倉庫管理が専用WMSか、基幹の機能か、物流委託先のシステムか等、実体をご教示ください。</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr"/>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>倉庫／POS／基幹</t>
+        </is>
+      </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>倉庫／POS／基幹</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
           <t>倉庫＝WMS決めつけ回避</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="50" customHeight="1">
+    <row r="10" ht="52" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
           <t>7</t>
@@ -922,254 +873,212 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>倉庫の実在庫の正は倉庫管理側、店舗の実在庫の正はPOS。基幹はそれらを集約して参照している</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>倉庫の実在庫は倉庫管理側、店舗の実在庫はPOSが正で、基幹はそれらを集約しているイメージで合っておりますか。</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr"/>
+          <t>倉庫の実在庫は倉庫管理側、店舗の実在庫はPOSが正で、基幹はそれらを集約している、という理解で相違ないでしょうか。</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr"/>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>基幹／倉庫／POS</t>
+        </is>
+      </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
+          <t>在庫の正</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="52" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>仕入・在庫</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>仕入発注は担当者が基幹で行っていると理解しております。アナログ発注や店舗発注が残っている場合は、その運用を教えてください。</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr"/>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>基幹</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>確認形</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="52" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>仕入・在庫</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>入荷後は倉庫管理／POSへ入荷入力し、その実績が基幹の在庫へ反映されると理解しております。棚卸タイミングで合わせる比重が大きい場合は、その旨をご教示ください。</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr"/>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
           <t>基幹／倉庫／POS</t>
         </is>
       </c>
-      <c r="G10" s="8" t="inlineStr">
-        <is>
-          <t>在庫の正</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="50" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>仕入・在庫</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>仕入発注は、イエローハット様／ジョイフル様の担当者が基幹で実施している（一部アナログの可能性あり）</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>仕入発注は、担当者が基幹で実施している理解で合っておりますか。アナログ発注が残っている場合や、店舗発注がある場合は差分を教えてください。</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="inlineStr"/>
-      <c r="F11" s="8" t="inlineStr">
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>入荷反映</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="52" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>受注・出荷</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>受注は電話・FAX・メールが中心で、担当者が基幹へ手入力していると理解しております。他の受注手段があれば教えてください。</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr"/>
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>基幹</t>
         </is>
       </c>
-      <c r="G11" s="8" t="inlineStr">
-        <is>
-          <t>オープンにせず確認形</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="50" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>仕入・在庫</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>入荷後は、倉庫管理／POSへ入荷入力し、その実績が基幹の在庫へ反映される（棚卸のみで合わせる運用ではない）</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>入荷後は、倉庫管理／POSへ入荷入力し、基幹へ在庫が反映される運用で合っておりますか。棚卸タイミングで合わせる比重が大きい場合は、その旨をご教示ください。</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr"/>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>資料既知の確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="64" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>受注・出荷</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>BtoB卸の出荷元は、取引先ごとに対応店舗が決まっており、倉庫またはその対応店舗から出荷していると考えております。この理解で相違ないでしょうか。異なる場合は、②倉庫出荷のみ（店舗関与はPhase2）／③その他、のどれに近いか、また①の場合の対応店舗の管理方法を教えてください。</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr"/>
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>基幹／倉庫／POS</t>
         </is>
       </c>
-      <c r="G12" s="8" t="inlineStr">
-        <is>
-          <t>入荷反映</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="50" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>出荷元</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="52" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>受注・出荷</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>受注は電話・FAX・メールが中心で、担当者が基幹へ手入力している</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>受注は電話・FAX・メールが中心で、担当者が基幹へ手入力している理解で合っておりますか。他の受注手段があれば教えてください。</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr"/>
-      <c r="F13" s="8" t="inlineStr">
-        <is>
-          <t>基幹</t>
-        </is>
-      </c>
-      <c r="G13" s="8" t="inlineStr">
-        <is>
-          <t>資料既知の確認止め</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="62" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>受注後の在庫引当は基幹を正として行い、倉庫管理／店舗側へ引当情報が連携されると理解しております。この流れで相違ないでしょうか。</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr"/>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>基幹／倉庫／POS</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>引当</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="52" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>受注・出荷</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>出荷元の理解：取引先ごとに対応店舗があり、倉庫または対応店舗から出荷している（卸が倉庫のみで店舗関与はPhase2、という可能性も残す）</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>BtoB卸の出荷元について、次の理解で合っておりますか。
-① 取引先ごとに対応店舗が決まっており、倉庫またはその対応店舗から出荷している
-合っていない場合は、②倉庫出荷のみ（店舗関与はPhase2）／③その他、のどれに近いか教えてください。①の場合、対応店舗の管理方法もご教示ください。</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr"/>
-      <c r="F14" s="8" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>受注後は基幹から倉庫または対応店舗へ出荷指示を出していると理解しております。指示手段（画面／CSV／紙・電話等）に違いがあれば教えてください。</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr"/>
+      <c r="E16" s="8" t="inlineStr">
         <is>
           <t>基幹／倉庫／POS</t>
         </is>
       </c>
-      <c r="G14" s="8" t="inlineStr">
-        <is>
-          <t>出荷元</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="50" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>出荷指示</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="52" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>受注・出荷</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>受注後の在庫引当は基幹を正として行い、倉庫管理／対応店舗（POS等）へ引当情報が連携される</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>受注後の在庫引当は基幹を正として行い、倉庫管理／店舗側へ引当情報が連携される理解で合っておりますか。</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="inlineStr"/>
-      <c r="F15" s="8" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>出荷実績の登録・在庫減算は倉庫管理／POS側で行い、基幹へ反映されると理解しております。この流れで相違ないでしょうか。</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr"/>
+      <c r="E17" s="8" t="inlineStr">
         <is>
           <t>基幹／倉庫／POS</t>
         </is>
       </c>
-      <c r="G15" s="8" t="inlineStr">
-        <is>
-          <t>引当</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="50" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="B16" s="11" t="inlineStr">
-        <is>
-          <t>受注・出荷</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>受注後、基幹から倉庫または対応店舗へ出荷指示を出している</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>受注後は、基幹から倉庫または対応店舗へ出荷指示を出している理解で合っておりますか。指示手段（画面／CSV／紙・電話等）に違いがあれば教えてください。</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr"/>
-      <c r="F16" s="8" t="inlineStr">
-        <is>
-          <t>基幹／倉庫／POS</t>
-        </is>
-      </c>
-      <c r="G16" s="8" t="inlineStr">
-        <is>
-          <t>出荷指示</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="50" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>受注・出荷</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>出荷実績・在庫減算は倉庫管理／POS側で登録し、基幹へ反映される</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>出荷実績の登録・在庫減算は、倉庫管理／POS側で実施し、基幹へ反映される理解で合っておりますか。</t>
-        </is>
-      </c>
-      <c r="E17" s="7" t="inlineStr"/>
       <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t>基幹／倉庫／POS</t>
-        </is>
-      </c>
-      <c r="G17" s="8" t="inlineStr">
         <is>
           <t>出荷実績</t>
         </is>
@@ -1178,16 +1087,16 @@
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>マスタは「どのシステムで管理（正）しているか」を明确化済み（商品＝基幹、顧客＝基幹、適合＝適合システム）。質問はすべて確認形。</t>
+          <t>マスタは管理システムを明示（商品＝基幹、顧客＝基幹、適合＝適合システム）。重点：①卸の管理主体 ②倉庫・在庫の実体と正 ③出荷元（対応店舗か倉庫のみか）</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:G17"/>
+  <autoFilter ref="A3:F17"/>
   <mergeCells count="3">
-    <mergeCell ref="A19:G19"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/knowledge/自動車アフターマーケット・部品卸/イエローハット_資料/ASIS_Phase1_確認質問票.xlsx
+++ b/knowledge/自動車アフターマーケット・部品卸/イエローハット_資料/ASIS_Phase1_確認質問票.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="図3_受注引当出荷" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'確認質問票'!$A$3:$F$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'確認質問票'!$A$3:$F$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -63,8 +63,14 @@
       <color rgb="00FFFFFF"/>
       <sz val="12"/>
     </font>
+    <font>
+      <name val="Yu Gothic"/>
+      <b val="1"/>
+      <color rgb="007A3A10"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -111,8 +117,13 @@
         <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4B183"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -134,11 +145,55 @@
         <color rgb="00B0B0B0"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B0B0B0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B0B0B0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B0B0B0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B0B0B0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B0B0B0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B0B0B0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B0B0B0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B0B0B0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -180,6 +235,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -279,6 +343,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -309,6 +376,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -339,6 +409,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -635,7 +708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1084,19 +1157,117 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>マスタは管理システムを明示（商品＝基幹、顧客＝基幹、適合＝適合システム）。重点：①卸の管理主体 ②倉庫・在庫の実体と正 ③出荷元（対応店舗か倉庫のみか）</t>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>受領資料の要望に対する認識確認</t>
+        </is>
+      </c>
+      <c r="B18" s="18" t="n"/>
+      <c r="C18" s="18" t="n"/>
+      <c r="D18" s="18" t="n"/>
+      <c r="E18" s="18" t="n"/>
+      <c r="F18" s="19" t="n"/>
+    </row>
+    <row r="19" ht="72" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>要望確認</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>資料では、店舗在庫・倉庫・メーカー／サプライヤー直送など、複数の仕入・出荷ルートが存在すると理解しております。ECではサプライヤー（拠点）単位でルートを扱い、拠点ごとに送料・リードタイム等を設定する想定です。現在のルートはこの整理で捉えられるか、標準的な拠点設定では表現できない例外ルールがあればご教示ください。</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr"/>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>基幹／倉庫／POS／仕入先</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>仕入・物流ルート</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="78" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>要望確認</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>資料では原価計算が手作業とあるため、原価・粗利をEC上で保持・参照したい要望と理解しております。
+保持する場合は、まず「サプライヤー×SKU単位の一律原価（改定時に更新）」を想定しております。この粒度で十分でしょうか。それとも、入荷ロット・仕入日・在庫単位など、個別原価の管理が必要でしょうか。</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr"/>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>基幹／原価管理</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>原価粒度</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="72" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t>要望確認</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>属人化している業務は、主に①取引先別単価 ②在庫・納期確認 ③出荷元／送料判断 ④見積作成〜受注入力 ⑤原価・粗利計算、と理解しております。この認識で相違ないか、ほかに担当者判断へ依存している業務があればご教示ください。</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr"/>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>基幹／倉庫／POS</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>属人化対象</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>要望確認の狙い：対応可否を断定する前に、①ルートの例外 ②必要な原価粒度 ③属人化の対象範囲、を先方と揃える。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:F17"/>
-  <mergeCells count="3">
-    <mergeCell ref="A19:F19"/>
+  <autoFilter ref="A3:F21"/>
+  <mergeCells count="4">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A18:F18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
